--- a/Unidad 1/G5_Matriz_IREB_V3.0.xlsx
+++ b/Unidad 1/G5_Matriz_IREB_V3.0.xlsx
@@ -15,7 +15,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="CHvvgMB4lX0mngcJp7PEw/KUxu12lOwT1XJXnK/IBko="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="s42ZbGqSrvqpKaNjXIrFKvO5oP0jLww5kBx3dq07qz4="/>
     </ext>
   </extLst>
 </workbook>
@@ -459,7 +459,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="100">
   <si>
     <t>MATRIZ PARA COMPROBACIÓN REQUERIMIENTOS DE CALIDAD DE PROYECTO ACADEMICO</t>
   </si>
@@ -606,25 +606,25 @@
     <t>AUTOR:</t>
   </si>
   <si>
-    <t>Nelson David Andino Martínez</t>
+    <t>Ricardo Lainez</t>
   </si>
   <si>
     <t>Marco Adrian Padilla Triviño</t>
   </si>
   <si>
+    <t>Nelson David Andino Martínez</t>
+  </si>
+  <si>
     <t>REQUERIMIENTOS EVALUADOS :</t>
+  </si>
+  <si>
+    <t>CU 01 Tomar pedido en mesa</t>
   </si>
   <si>
     <t xml:space="preserve">CU 04 Gestionar Preparación del Pedido </t>
   </si>
   <si>
-    <t>Ricardo Lainez</t>
-  </si>
-  <si>
     <t>CONTENIDO</t>
-  </si>
-  <si>
-    <t>CU 01 Tomar pedido en mesa</t>
   </si>
   <si>
     <t>No.</t>
@@ -717,16 +717,10 @@
     <t>RECOMENDACIÓN</t>
   </si>
   <si>
-    <t>¿Se ha incorporado los cambios sugeridos por el tutor o el cliente?</t>
+    <t>¿Se han validado y aprobado formalmente todos los entregables de la entrevista (videoconferencia, minuta, acta de aceptación)?</t>
   </si>
   <si>
-    <t>Se recomienda programar una sesión de revisión con el cliente para validar el flujo. Dado que el nivel de detalle y precisión del sistema ya se encuentra debidamente documentado en el SRS, el objetivo de esta reunión es obtener el acuerdo de conformidad definitivo por parte de los interesados.</t>
-  </si>
-  <si>
-    <t>¿Se mantiene la coherencia con otros requisitos del sistema y utiliza términos o definiciones de forma uniforme a lo largo del documento?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se recomienda unificar los estados del pedido (como pendiente, en preparación, listo y listo para entregar) en todo el documento, ya que actualmente hay contradicciones importantes entre los niveles. Por ejemplo, en el nivel alto esta que el cocinero pone el pedido en "listo para entregar", pero en el detalle de caja el sistema cambia a ese mismo estado recién después de que el cliente paga. </t>
+    <t>Elaborar y firmar un acta de validación definitiva con el cliente que certifique la funcionalidad del mesero al registrar órdenes presenciales. Dado que en la matriz IREB se detectó que falta incorporar los últimos cambios solicitados en el feedback, esta acta debe servir como mecanismo para confirmar formalmente que las reglas de negocio del caso de uso han sido actualizadas y aprobadas por todas las partes.</t>
   </si>
   <si>
     <t>¿Se han definido criterios de aceptación y casos de prueba
@@ -734,13 +728,28 @@
 requisito?</t>
   </si>
   <si>
-    <t>Se recomienda solventar la ausencia de casos de prueba formales mediante su diseño y documentación. Es prioritario estructurar los casos de prueba necesarios para validar tanto los flujos básicos como los alternativos descritos en el SRS</t>
+    <t>Puesto que la matriz de calidad señala explícitamente la falta de casos de prueba, se recomienda diseñar de inmediato un set de pruebas enfocado en el flujo de toma de pedidos. Para esto, define criterios de aceptación específicos y medibles basados en el alcance del caso de uso, tales como: verificar que el sistema restrinja el envío a cocina si la orden no contiene al menos un producto, y comprobar que el sistema asigne correctamente el estado inicial "pendiente" una vez guardado el pedido.</t>
+  </si>
+  <si>
+    <t>¿Se ha incorporado los cambios sugeridos por el tutor o el cliente?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar una sesión de revisión formal para consolidar el último feedback del cliente en el CU 03, actualizando la descripción del flujo, validaciones de mesa/QR y registrando los ajustes en la tabla de control de versiones del ERS.   </t>
+  </si>
+  <si>
+    <t>¿Se mantiene la coherencia con otros requisitos del sistema y utiliza términos o definiciones de forma uniforme a lo largo del documento?</t>
+  </si>
+  <si>
+    <t>Estandarizar la nomenclatura entre la matriz de trazabilidad y el catálogo de requisitos funcionales (alinear las subfunciones CU 3.1 a CU 3.3 con RF-04), evitando redundancias de términos y homologando el estado inicial del pedido con el módulo de cocina.</t>
+  </si>
+  <si>
+    <t>Diseñar y adjuntar la matriz de casos de prueba detallada para el flujo de escaneo QR y confirmación de pedido, incorporando criterios de aceptación medibles sobre tiempos de respuesta y manejo de fallos de red en el móvil.</t>
   </si>
   <si>
     <t>¿Todos los requerimientos  han sido acordados con todos los interesados?</t>
   </si>
   <si>
-    <t>Se recomienda realizar una minuta o acta firmada por las partes clave, incluyendo a la gerencia del proyecto y los analistas. Esto asegurará que la versión final del caso de uso, con los cambios del cliente ya aplicados, tenga el respaldo oficial antes de avanzar al diseño y desarrollo.</t>
+    <t>Formalizar un acta de cierre y aprobación final firmada por el cliente y el equipo del proyecto, garantizando que los cambios acordados en las videoconferencias queden ratificados por todas las partes interesadas antes del paso a desarrollo.</t>
   </si>
   <si>
     <t>¿Se contempla de manera explícita la secuencia completa de los estados de preparación en el caso de uso y su impacto en la vista del cliente?</t>
@@ -749,28 +758,16 @@
     <t>Se recomienda detallar de forma más estricta en el flujo del CU 004.1 las transiciones exactas de los estados ("pendiente" -&gt; "en preparación" -&gt; "listo" -&gt; "listo para entregar"), especificando los tiempos máximos permitidos para cada cambio de estado y asegurando que el cliente reciba la notificación visual en tiempo real en el aplicativo web sin demoras de sincronización.</t>
   </si>
   <si>
-    <t xml:space="preserve">Realizar una sesión de revisión formal para consolidar el último feedback del cliente en el CU 03, actualizando la descripción del flujo, validaciones de mesa/QR y registrando los ajustes en la tabla de control de versiones del ERS.   </t>
-  </si>
-  <si>
     <t>¿El caso de uso considera el manejo de excepciones y errores operativos en cocina (por ejemplo, rechazo de un plato por falta de stock de ingredientes o cancelación de un pedido por parte del cliente)?</t>
   </si>
   <si>
     <t>Se recomienda incorporar flujos alternativos dentro del CU 004.1 que expliquen detalladamente cómo debe proceder el cocinero si un producto no se puede preparar, cómo se comunica la cancelación o modificación del pedido a la caja o al mesero, y cómo se actualiza el stock o la base de datos para evitar discrepancias operativas.</t>
   </si>
   <si>
-    <t>Estandarizar la nomenclatura entre la matriz de trazabilidad y el catálogo de requisitos funcionales (alinear las subfunciones CU 3.1 a CU 3.3 con RF-04), evitando redundancias de términos y homologando el estado inicial del pedido con el módulo de cocina.</t>
-  </si>
-  <si>
     <t>¿Se han definido los casos de prueba funcionales y de rendimiento específicos para validar la concurrencia en la bandeja de pedidos del cocinero?</t>
   </si>
   <si>
-    <t>Diseñar y adjuntar la matriz de casos de prueba detallada para el flujo de escaneo QR y confirmación de pedido, incorporando criterios de aceptación medibles sobre tiempos de respuesta y manejo de fallos de red en el móvil.</t>
-  </si>
-  <si>
     <t>Se recomienda elaborar casos de prueba técnicos orientados al rendimiento del módulo de cocina (CU 004.1), simulando la llegada simultánea de múltiples pedidos desde diferentes canales (mesa, QR y teléfono) para verificar que el sistema no sufra bloqueos, mantenga el orden cronológico y cumpla con la latencia requerida en la interfaz del cocinero.</t>
-  </si>
-  <si>
-    <t>Formalizar un acta de cierre y aprobación final firmada por el cliente y el equipo del proyecto, garantizando que los cambios acordados en las videoconferencias queden ratificados por todas las partes interesadas antes del paso a desarrollo.</t>
   </si>
   <si>
     <t>¿El diseño de la interfaz y las acciones del cocinero en el CU 004.1 están alineadas con las restricciones de hardware y ergonomía del entorno de cocina?</t>
@@ -1091,7 +1088,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1242,16 +1239,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -1260,10 +1254,16 @@
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -1455,6 +1455,12 @@
     </dxf>
   </dxfs>
   <tableStyles count="9">
+    <tableStyle count="4" pivot="0" name="MODELO LISTA DE COMPROBACION - -style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
     <tableStyle count="4" pivot="0" name="MODELO DE LISTA DE COMPROBACION-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
@@ -1466,18 +1472,6 @@
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
-    </tableStyle>
-    <tableStyle count="4" pivot="0" name="MODELO LISTA DE COMPROBACION - -style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
-    </tableStyle>
-    <tableStyle count="4" pivot="0" name="MODELO DE LISTA DE COMPROBACION-style 2">
-      <tableStyleElement dxfId="5" type="headerRow"/>
-      <tableStyleElement dxfId="6" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="7" size="0" type="wholeTable"/>
     </tableStyle>
     <tableStyle count="4" pivot="0" name="Hoja 1-style 2">
       <tableStyleElement dxfId="5" type="headerRow"/>
@@ -1491,11 +1485,11 @@
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="7" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="MODELO DE LISTA DE COMPROBACION-style 3">
-      <tableStyleElement dxfId="8" type="headerRow"/>
-      <tableStyleElement dxfId="9" type="firstRowStripe"/>
+    <tableStyle count="4" pivot="0" name="MODELO DE LISTA DE COMPROBACION-style 2">
+      <tableStyleElement dxfId="5" type="headerRow"/>
+      <tableStyleElement dxfId="6" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="10" size="0" type="wholeTable"/>
+      <tableStyleElement dxfId="7" size="0" type="wholeTable"/>
     </tableStyle>
     <tableStyle count="4" pivot="0" name="Hoja 1-style 3">
       <tableStyleElement dxfId="8" type="headerRow"/>
@@ -1504,6 +1498,12 @@
       <tableStyleElement dxfId="10" size="0" type="wholeTable"/>
     </tableStyle>
     <tableStyle count="4" pivot="0" name="MODELO LISTA DE COMPROBACION - -style 3">
+      <tableStyleElement dxfId="8" type="headerRow"/>
+      <tableStyleElement dxfId="9" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="10" size="0" type="wholeTable"/>
+    </tableStyle>
+    <tableStyle count="4" pivot="0" name="MODELO DE LISTA DE COMPROBACION-style 3">
       <tableStyleElement dxfId="8" type="headerRow"/>
       <tableStyleElement dxfId="9" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -1913,7 +1913,7 @@
     <xdr:ext cx="4286250" cy="2143125"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="677915408" name="Chart 3" title="Gráfico"/>
+        <xdr:cNvPr id="677915408" name="Chart 2" title="Gráfico"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1973,7 +1973,7 @@
     <xdr:ext cx="4286250" cy="2143125"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="928943876" name="Chart 2"/>
+        <xdr:cNvPr id="928943876" name="Chart 3"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2004,7 +2004,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A7:D16" displayName="Table_1" name="Table_1" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A7:D16" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="4">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Pregunta" id="2"/>
@@ -2028,7 +2028,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:D34" displayName="Table_3" name="Table_3" id="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:D34" displayName="Table_3" name="Table_3" id="8">
   <tableColumns count="4">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Pregunta" id="2"/>
@@ -2064,7 +2064,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:D34" displayName="Table_6" name="Table_6" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:D34" displayName="Table_6" name="Table_6" id="9">
   <tableColumns count="4">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Pregunta" id="2"/>
@@ -2076,7 +2076,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A7:D16" displayName="Table_7" name="Table_7" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A7:D16" displayName="Table_7" name="Table_7" id="3">
   <tableColumns count="4">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Pregunta" id="2"/>
@@ -2100,7 +2100,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:D34" displayName="Table_9" name="Table_9" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:D34" displayName="Table_9" name="Table_9" id="7">
   <tableColumns count="4">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Pregunta" id="2"/>
@@ -4178,21 +4178,21 @@
         <v>43</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6">
       <c r="A6" s="34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -5669,7 +5669,7 @@
     </row>
     <row r="4" ht="21.0" customHeight="1">
       <c r="B4" s="31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" s="33" t="s">
         <v>8</v>
@@ -5678,7 +5678,7 @@
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="42.0" customHeight="1">
       <c r="A6" s="34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -7148,21 +7148,21 @@
         <v>43</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" ht="29.25" customHeight="1">
       <c r="B4" s="31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="21.0" customHeight="1">
       <c r="A6" s="34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" ht="24.0" customHeight="1">
@@ -8606,29 +8606,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="13" t="s">
         <v>83</v>
       </c>
       <c r="B3" s="58" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="4" ht="56.25" customHeight="1">
-      <c r="A4" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B4" s="58" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="58" t="s">
-        <v>88</v>
-      </c>
-    </row>
+    <row r="4" ht="14.25" customHeight="1"/>
+    <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="14.25" customHeight="1"/>
     <row r="7" ht="14.25" customHeight="1"/>
     <row r="8" ht="14.25" customHeight="1"/>
@@ -8840,7 +8826,7 @@
     <row r="214" ht="14.25" customHeight="1"/>
     <row r="215" ht="14.25" customHeight="1"/>
     <row r="216" ht="14.25" customHeight="1"/>
-    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
     <row r="218" ht="15.75" customHeight="1"/>
     <row r="219" ht="15.75" customHeight="1"/>
     <row r="220" ht="15.75" customHeight="1"/>
@@ -9620,7 +9606,6 @@
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -9650,35 +9635,35 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="61" t="s">
-        <v>91</v>
+      <c r="A2" s="59" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="57" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="62" t="s">
-        <v>94</v>
+      <c r="A3" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="61" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B4" s="62" t="s">
-        <v>96</v>
+        <v>83</v>
+      </c>
+      <c r="B4" s="61" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="64" t="s">
-        <v>98</v>
+      <c r="A5" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1"/>
@@ -10705,35 +10690,35 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="60" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="61" t="s">
-        <v>90</v>
+      <c r="A2" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="60" t="s">
-        <v>92</v>
-      </c>
-      <c r="B3" s="62" t="s">
-        <v>93</v>
+      <c r="A3" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="61" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="63" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="64" t="s">
+      <c r="A4" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="63" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="66" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="63" t="s">
         <v>99</v>
-      </c>
-      <c r="B5" s="64" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1"/>

--- a/Unidad 1/G5_Matriz_IREB_V3.0.xlsx
+++ b/Unidad 1/G5_Matriz_IREB_V3.0.xlsx
@@ -887,13 +887,14 @@
     <t>Realizable</t>
   </si>
   <si>
-    <t>1. Funcionalidad tomada en cuenta dentro de la estimación del costo del proyecto (900$)
-2. No se ha desarrollado</t>
+    <t>1. Funcionalidad considerada en la estimación del proyecto (144 horas por integrante, costeo por hora según el rol).
+2. Tecnologías y hardware mínimo definidos en la ERS (secciones 3.1.6 a 3.1.11): React + Vite, Node.js con Express, servicios REST con JSON.
+3. Su construcción está planificada para las fases posteriores al análisis y diseño.</t>
   </si>
   <si>
     <t>1. Funcionalidad considerada en la estimación del proyecto (144 horas por integrante, costeo por hora según el rol).
 2. Tecnologías y hardware mínimo definidos en la ERS (secciones 3.1.6 a 3.1.11): React + Vite, Node.js con Express, servicios REST con JSON.
-3. Aún no se ha desarrollado.</t>
+3. Su construcción está planificada para las fases posteriores al análisis y diseño.</t>
   </si>
   <si>
     <t>Traceable</t>
